--- a/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output3.xlsx
+++ b/Techniques/Model based and Residual Monitoring/outputs/G11/dsas_g11_lubrication_system_deviation_monitoring/deviation_monitoring/dsas_g11_lubrication_system_deviation_monitoring_output3.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P67"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,11 @@
           <t>Is_Anomaly</t>
         </is>
       </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Anomaly_Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -565,6 +570,11 @@
       <c r="P2" t="b">
         <v>0</v>
       </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -617,6 +627,11 @@
       <c r="P3" t="b">
         <v>0</v>
       </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -669,6 +684,11 @@
       <c r="P4" t="b">
         <v>0</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -721,6 +741,11 @@
       <c r="P5" t="b">
         <v>0</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -773,6 +798,11 @@
       <c r="P6" t="b">
         <v>0</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -825,6 +855,11 @@
       <c r="P7" t="b">
         <v>0</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -877,6 +912,11 @@
       <c r="P8" t="b">
         <v>0</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -929,6 +969,11 @@
       <c r="P9" t="b">
         <v>0</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -981,6 +1026,11 @@
       <c r="P10" t="b">
         <v>0</v>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1033,6 +1083,11 @@
       <c r="P11" t="b">
         <v>0</v>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1085,6 +1140,11 @@
       <c r="P12" t="b">
         <v>0</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1137,6 +1197,11 @@
       <c r="P13" t="b">
         <v>0</v>
       </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1189,6 +1254,11 @@
       <c r="P14" t="b">
         <v>0</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1241,6 +1311,11 @@
       <c r="P15" t="b">
         <v>0</v>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1293,6 +1368,11 @@
       <c r="P16" t="b">
         <v>0</v>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1345,6 +1425,11 @@
       <c r="P17" t="b">
         <v>0</v>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1397,6 +1482,11 @@
       <c r="P18" t="b">
         <v>0</v>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1449,6 +1539,11 @@
       <c r="P19" t="b">
         <v>0</v>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1501,6 +1596,11 @@
       <c r="P20" t="b">
         <v>0</v>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1553,6 +1653,11 @@
       <c r="P21" t="b">
         <v>0</v>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1605,6 +1710,11 @@
       <c r="P22" t="b">
         <v>0</v>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1657,6 +1767,11 @@
       <c r="P23" t="b">
         <v>0</v>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1709,6 +1824,11 @@
       <c r="P24" t="b">
         <v>0</v>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1761,6 +1881,11 @@
       <c r="P25" t="b">
         <v>0</v>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1813,6 +1938,11 @@
       <c r="P26" t="b">
         <v>0</v>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1865,6 +1995,11 @@
       <c r="P27" t="b">
         <v>0</v>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1917,6 +2052,11 @@
       <c r="P28" t="b">
         <v>0</v>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1969,6 +2109,11 @@
       <c r="P29" t="b">
         <v>0</v>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2021,6 +2166,11 @@
       <c r="P30" t="b">
         <v>0</v>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2073,6 +2223,11 @@
       <c r="P31" t="b">
         <v>0</v>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2125,6 +2280,11 @@
       <c r="P32" t="b">
         <v>0</v>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2177,6 +2337,11 @@
       <c r="P33" t="b">
         <v>0</v>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2229,6 +2394,11 @@
       <c r="P34" t="b">
         <v>0</v>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2281,6 +2451,11 @@
       <c r="P35" t="b">
         <v>0</v>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2333,6 +2508,11 @@
       <c r="P36" t="b">
         <v>0</v>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2385,6 +2565,11 @@
       <c r="P37" t="b">
         <v>0</v>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2437,6 +2622,11 @@
       <c r="P38" t="b">
         <v>0</v>
       </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2489,6 +2679,11 @@
       <c r="P39" t="b">
         <v>0</v>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2541,6 +2736,11 @@
       <c r="P40" t="b">
         <v>0</v>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2593,6 +2793,11 @@
       <c r="P41" t="b">
         <v>0</v>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2645,6 +2850,11 @@
       <c r="P42" t="b">
         <v>0</v>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2697,6 +2907,11 @@
       <c r="P43" t="b">
         <v>0</v>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2749,6 +2964,11 @@
       <c r="P44" t="b">
         <v>0</v>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -2801,6 +3021,11 @@
       <c r="P45" t="b">
         <v>0</v>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -2853,6 +3078,11 @@
       <c r="P46" t="b">
         <v>0</v>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2905,6 +3135,11 @@
       <c r="P47" t="b">
         <v>0</v>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -2957,6 +3192,11 @@
       <c r="P48" t="b">
         <v>0</v>
       </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3009,6 +3249,11 @@
       <c r="P49" t="b">
         <v>0</v>
       </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3061,6 +3306,11 @@
       <c r="P50" t="b">
         <v>0</v>
       </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3113,6 +3363,11 @@
       <c r="P51" t="b">
         <v>0</v>
       </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3165,6 +3420,11 @@
       <c r="P52" t="b">
         <v>0</v>
       </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3217,6 +3477,11 @@
       <c r="P53" t="b">
         <v>0</v>
       </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3269,6 +3534,11 @@
       <c r="P54" t="b">
         <v>0</v>
       </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3321,6 +3591,11 @@
       <c r="P55" t="b">
         <v>0</v>
       </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3373,6 +3648,11 @@
       <c r="P56" t="b">
         <v>1</v>
       </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>⚠️ Anomaly</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3425,6 +3705,11 @@
       <c r="P57" t="b">
         <v>0</v>
       </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3477,6 +3762,11 @@
       <c r="P58" t="b">
         <v>0</v>
       </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3529,6 +3819,11 @@
       <c r="P59" t="b">
         <v>0</v>
       </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3581,6 +3876,11 @@
       <c r="P60" t="b">
         <v>0</v>
       </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3633,6 +3933,11 @@
       <c r="P61" t="b">
         <v>0</v>
       </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -3685,6 +3990,11 @@
       <c r="P62" t="b">
         <v>0</v>
       </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -3737,6 +4047,11 @@
       <c r="P63" t="b">
         <v>0</v>
       </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -3789,6 +4104,11 @@
       <c r="P64" t="b">
         <v>0</v>
       </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -3841,6 +4161,11 @@
       <c r="P65" t="b">
         <v>0</v>
       </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -3893,6 +4218,11 @@
       <c r="P66" t="b">
         <v>0</v>
       </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -3944,6 +4274,11 @@
       </c>
       <c r="P67" t="b">
         <v>0</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>✅ Normal</t>
+        </is>
       </c>
     </row>
   </sheetData>
